--- a/DIR FDE-feature-detection-engine.xlsx
+++ b/DIR FDE-feature-detection-engine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FDE-feature-detection-engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DC1A218-BD06-42EF-90D6-9579F88C8C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6673DE-0423-4D9F-90E3-933B697FCB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24042" windowHeight="12797" xr2:uid="{40FF3AB3-20B7-452B-8E79-4A1B33D1F039}"/>
+    <workbookView xWindow="0" yWindow="363" windowWidth="24267" windowHeight="13023" xr2:uid="{40FF3AB3-20B7-452B-8E79-4A1B33D1F039}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
